--- a/public/templates/product_import_template.xlsx
+++ b/public/templates/product_import_template.xlsx
@@ -15,14 +15,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="19">
   <si>
     <t>Product Name</t>
   </si>
   <si>
-    <t>Product Code</t>
-  </si>
-  <si>
     <t>Price</t>
   </si>
   <si>
@@ -41,9 +38,6 @@
     <t>Smartphone Wireless Pro</t>
   </si>
   <si>
-    <t>PROD-MPHONE-01</t>
-  </si>
-  <si>
     <t>Electronics</t>
   </si>
   <si>
@@ -56,9 +50,6 @@
     <t>Ergonomic Office Chair</t>
   </si>
   <si>
-    <t>PROD-CHAIR-02</t>
-  </si>
-  <si>
     <t>Furniture</t>
   </si>
   <si>
@@ -68,9 +59,6 @@
     <t>Organic Green Tea</t>
   </si>
   <si>
-    <t>PROD-TEA-03</t>
-  </si>
-  <si>
     <t>Food &amp; Beverage</t>
   </si>
   <si>
@@ -78,9 +66,6 @@
   </si>
   <si>
     <t>Mechanical Keyboard RGB</t>
-  </si>
-  <si>
-    <t>PROD-KEYBOARD-04</t>
   </si>
   <si>
     <t>false</t>
@@ -426,19 +411,18 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="28.136" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="19.995" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="16.425" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="11.711" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="80.123" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="10.569" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="16.425" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="11.711" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="80.123" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -457,100 +441,85 @@
       <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
+      <c r="B2">
+        <v>12000000</v>
+      </c>
+      <c r="C2">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3">
+        <v>1500000</v>
+      </c>
+      <c r="C3">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4">
+        <v>45000</v>
+      </c>
+      <c r="C4">
+        <v>120</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>850000</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
         <v>7</v>
       </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
-        <v>12000000</v>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>1500000</v>
-      </c>
-      <c r="D3">
-        <v>15</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="E5" t="s">
         <v>17</v>
       </c>
-      <c r="C4">
-        <v>45000</v>
-      </c>
-      <c r="D4">
-        <v>120</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F5" t="s">
         <v>18</v>
-      </c>
-      <c r="F4" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5">
-        <v>850000</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
